--- a/output/pdf_financials_xlsx/WSK.xlsx
+++ b/output/pdf_financials_xlsx/WSK.xlsx
@@ -4506,16 +4506,16 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.001929</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.001918</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.005411</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.004926</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0</v>
@@ -4549,40 +4549,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>9.76487</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>9.764046</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>9.764046</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>9.764046</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>9.764046</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>9.953777000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>10.072391</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.163462</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.324173</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>10.324173</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.324173</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>10.456904</v>
       </c>
     </row>
     <row r="93">
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>12.186775</v>
+        <v>12.168213</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -5730,25 +5730,25 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.268853</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>0.041881</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.051354</v>
+        <v>-0.161141</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.212785</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.06647400000000001</v>
+        <v>0.052247</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>1e-06</v>
+        <v>-0.006819</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.424427</v>
+        <v>0.349007</v>
       </c>
     </row>
     <row r="119">
@@ -7628,7 +7628,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -8348,7 +8352,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -8642,7 +8650,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -9826,7 +9838,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -11020,7 +11036,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>9.76487</v>
       </c>
@@ -11086,7 +11106,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>-0.001929</v>
       </c>
@@ -12688,7 +12712,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -22246,7 +22274,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WSK.xlsx
+++ b/output/pdf_financials_xlsx/WSK.xlsx
@@ -827,34 +827,34 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.307106</v>
+        <v>0.729449</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.010909</v>
+        <v>0.323921</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.046647</v>
+        <v>0.456954</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.003507</v>
+        <v>0.848163</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.34558</v>
+        <v>0.7179219999999999</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.376211</v>
+        <v>0.579697</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.380492</v>
+        <v>0.906186</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.954543</v>
+        <v>0.722209</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.722186</v>
+        <v>0.570305</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.621045</v>
+        <v>0.921376</v>
       </c>
     </row>
     <row r="11">
@@ -874,34 +874,34 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.307106</v>
+        <v>-0.729449</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.010909</v>
+        <v>-0.323921</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.046647</v>
+        <v>-0.456954</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.003507</v>
+        <v>-0.848163</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.34558</v>
+        <v>-0.7179219999999999</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.376211</v>
+        <v>-0.579697</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.380492</v>
+        <v>-0.906186</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.954543</v>
+        <v>-0.722209</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.722186</v>
+        <v>-0.570305</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.621045</v>
+        <v>-0.921376</v>
       </c>
     </row>
     <row r="12">
@@ -921,34 +921,34 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006469</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003309</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002225</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.004007</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00478</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.026182</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.126461</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.114035</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.058106</v>
       </c>
     </row>
     <row r="13">
@@ -1672,34 +1672,34 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-13.131336</v>
+        <v>-13.137805</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.313012</v>
+        <v>-0.316321</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.410307</v>
+        <v>-0.412532</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.844656</v>
+        <v>-0.8486629999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.372342</v>
+        <v>-0.377122</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.7965140000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.286678</v>
+        <v>-3.31286</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.676752</v>
+        <v>-2.803213</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.292491</v>
+        <v>-1.406526</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.602349</v>
+        <v>-0.660455</v>
       </c>
     </row>
     <row r="28">
@@ -1766,34 +1766,34 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-13.131336</v>
+        <v>-13.137805</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.313012</v>
+        <v>-0.316321</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.410307</v>
+        <v>-0.412532</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.844656</v>
+        <v>-0.8486629999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.372342</v>
+        <v>-0.377122</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.7965140000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.286678</v>
+        <v>-3.31286</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.676752</v>
+        <v>-2.803213</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.292491</v>
+        <v>-1.406526</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.602349</v>
+        <v>-0.660455</v>
       </c>
     </row>
     <row r="30">
@@ -2003,16 +2003,16 @@
         <v>0.271304</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.025796</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.176915</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.169901</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.367438</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.665207</v>
@@ -2089,16 +2089,16 @@
         <v>0.271304</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.025796</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.176915</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.169901</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.367438</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>3.665207</v>
@@ -2605,16 +2605,16 @@
         <v>0.009168000000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.035829</v>
+        <v>0.010033</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.184725</v>
+        <v>0.00781</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.927208</v>
+        <v>1.757307</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9.703013</v>
+        <v>8.335575</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>4.508522</v>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -23621,31 +23621,31 @@
         </is>
       </c>
       <c r="H229" s="5" t="n">
-        <v>-0.323921</v>
+        <v>0.323921</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>-0.456954</v>
+        <v>0.456954</v>
       </c>
       <c r="J229" s="5" t="n">
-        <v>-0.848163</v>
+        <v>0.848163</v>
       </c>
       <c r="K229" s="5" t="n">
-        <v>-0.7179219999999999</v>
+        <v>0.7179219999999999</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>-0.579697</v>
+        <v>0.579697</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>-0.906186</v>
+        <v>0.906186</v>
       </c>
       <c r="N229" s="5" t="n">
-        <v>-0.722209</v>
+        <v>0.722209</v>
       </c>
       <c r="O229" s="5" t="n">
-        <v>-0.570305</v>
+        <v>0.570305</v>
       </c>
       <c r="P229" s="5" t="n">
-        <v>-0.921376</v>
+        <v>0.921376</v>
       </c>
     </row>
     <row r="230">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -29624,10 +29624,10 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>-0.729449</v>
+        <v>0.729449</v>
       </c>
       <c r="H309" s="5" t="n">
-        <v>-0.319836</v>
+        <v>0.319836</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -29688,7 +29688,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">

--- a/output/pdf_financials_xlsx/WSK.xlsx
+++ b/output/pdf_financials_xlsx/WSK.xlsx
@@ -534,15 +534,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -581,15 +577,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -628,15 +620,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -675,45 +663,41 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.6817879999999999</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.444879</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.156428</v>
+        <v>0.20013</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.041377</v>
+        <v>0.026324</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.124572</v>
+        <v>0.144566</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.20186</v>
+        <v>0.221512</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.168</v>
+        <v>0.19723</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.198412</v>
+        <v>0.213412</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.263718</v>
+        <v>0.275718</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.391329</v>
+        <v>0.403329</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.34427</v>
+        <v>0.36027</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.608531</v>
+        <v>0.6215309999999999</v>
       </c>
     </row>
     <row r="8">
@@ -722,15 +706,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -769,15 +749,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.464466</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.225231</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.150678</v>
@@ -816,15 +792,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>1.146254</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.9352200000000001</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.729449</v>
@@ -863,15 +835,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-1.615219</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.93784</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.729449</v>
@@ -910,15 +878,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.020197</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.015138</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.006469</v>
@@ -957,15 +921,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1004,15 +964,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1051,15 +1007,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.275936</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.194222</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.066176</v>
@@ -1098,15 +1050,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-1.319086</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.72848</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-13.131336</v>
@@ -1145,15 +1093,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1326,15 +1270,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.319086</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.72848</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-13.131336</v>
@@ -1373,15 +1313,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1420,15 +1356,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1467,15 +1399,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-1.319086</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.72848</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-13.131336</v>
@@ -1514,15 +1442,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -1563,15 +1487,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -1661,15 +1581,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-1.339283</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.743618</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-13.137805</v>
@@ -1708,15 +1624,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1755,15 +1667,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.339283</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.743618</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-13.137805</v>
@@ -1869,15 +1777,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4817,15 +4721,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-1.319086</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.72848</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-13.131336</v>
@@ -4864,15 +4764,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -4911,15 +4807,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -4958,15 +4850,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -5005,15 +4893,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.134289</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.043234</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0.072216</v>
@@ -5052,15 +4936,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.002856</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.093885</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>0.111814</v>
@@ -5099,15 +4979,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -5146,15 +5022,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.942829</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.821985</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.443246</v>
@@ -5193,15 +5065,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.009565000000000001</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>-0.000107</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -5240,15 +5108,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -5287,15 +5151,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -5334,15 +5194,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -5381,15 +5237,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -5428,15 +5280,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -5475,15 +5323,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -5522,15 +5366,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -5569,15 +5409,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -5607,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.948498</v>
       </c>
     </row>
     <row r="116">
@@ -5616,15 +5452,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -5663,15 +5495,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -5710,15 +5538,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>-0.350156</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>-0.016446</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>12.168213</v>
@@ -5757,15 +5581,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.552029</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0.807187</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>0.052873</v>
@@ -5808,15 +5628,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -5855,15 +5671,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -5902,15 +5714,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -5949,15 +5757,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -5996,15 +5800,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -6043,15 +5843,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -6090,15 +5886,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -6204,15 +5996,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -6304,15 +6092,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>2.143684</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.673413</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>0.662462</v>
@@ -6351,15 +6135,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -6398,15 +6178,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-1.470271</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.010951</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>-0.38688</v>
@@ -6445,15 +6221,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.673413</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.662462</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.275582</v>
@@ -6492,15 +6264,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6597,7 +6365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P321"/>
+  <dimension ref="A1:P348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12003,15 +11771,11 @@
           <t>Amortization</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="5" t="n">
+        <v>0.003625</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.002414</v>
       </c>
       <c r="G74" s="5" t="n">
         <v>0.000828</v>
@@ -12636,7 +12400,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -15096,7 +14864,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -18339,15 +18111,11 @@
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E159" s="5" t="n">
+        <v>0.035675</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>0.038687</v>
       </c>
       <c r="G159" s="5" t="n">
         <v>0.0287</v>
@@ -21665,15 +21433,11 @@
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E203" s="5" t="n">
+        <v>-1.106453</v>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>-0.684866</v>
       </c>
       <c r="G203" s="5" t="n">
         <v>-0.6272759999999999</v>
@@ -21743,15 +21507,11 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E204" s="5" t="n">
+        <v>0.134289</v>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>-0.043234</v>
       </c>
       <c r="G204" s="5" t="n">
         <v>0.072216</v>
@@ -21821,15 +21581,11 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E205" s="5" t="n">
+        <v>0.002856</v>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>-0.093885</v>
       </c>
       <c r="G205" s="5" t="n">
         <v>0.111814</v>
@@ -21975,15 +21731,11 @@
           <t>ChangeInWorkingCapital</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E207" s="5" t="n">
+        <v>-0.942829</v>
+      </c>
+      <c r="F207" s="5" t="n">
+        <v>-0.821985</v>
       </c>
       <c r="G207" s="5" t="n">
         <v>-0.443246</v>
@@ -22279,15 +22031,11 @@
           <t>NetOtherInvestingChanges</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E211" s="5" t="n">
+        <v>-0.350156</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>-0.016446</v>
       </c>
       <c r="G211" s="5" t="n">
         <v>-0.018562</v>
@@ -22355,15 +22103,11 @@
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E212" s="5" t="n">
+        <v>-0.807353</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>0.822353</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -22435,15 +22179,11 @@
           <t>InvestingCashFlow</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E213" s="5" t="n">
+        <v>-0.552029</v>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>0.807187</v>
       </c>
       <c r="G213" s="5" t="n">
         <v>0.052873</v>
@@ -22509,15 +22249,11 @@
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E214" s="5" t="n">
+        <v>0.024587</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>0.003847</v>
       </c>
       <c r="G214" s="5" t="n">
         <v>0.003493</v>
@@ -22587,15 +22323,11 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E215" s="5" t="n">
+        <v>-1.470271</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>-0.010951</v>
       </c>
       <c r="G215" s="5" t="n">
         <v>-0.38688</v>
@@ -22665,15 +22397,11 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E216" s="5" t="n">
+        <v>2.143684</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>0.673413</v>
       </c>
       <c r="G216" s="5" t="n">
         <v>0.662462</v>
@@ -22743,15 +22471,11 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E217" s="5" t="n">
+        <v>0.673413</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>0.662462</v>
       </c>
       <c r="G217" s="5" t="n">
         <v>0.275582</v>
@@ -22803,22 +22527,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Amortization $</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -22826,15 +22550,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F218" s="5" t="n">
+        <v>-0.72848</v>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>-13.131336</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -22871,8 +22591,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O218" s="5" t="n">
-        <v>0.005107</v>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
@@ -22883,33 +22605,29 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Consulting fees 7</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="n">
+        <v>0.009565000000000001</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>-0.000107</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -22956,24 +22674,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P219" s="5" t="n">
-        <v>0.15</v>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Director fees 7</t>
+          <t>(Gain) loss on disposal of equipment</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -22982,15 +22702,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F220" s="5" t="n">
+        <v>0.00262</v>
+      </c>
+      <c r="G220" s="5" t="n">
+        <v>-0.009233</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -23027,34 +22743,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O220" s="5" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="P220" s="5" t="n">
-        <v>0.013</v>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Filing and transfer agent</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Write-off of equipment</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -23065,58 +22781,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="n">
-        <v>0.012547</v>
-      </c>
-      <c r="I221" s="5" t="n">
-        <v>0.016651</v>
-      </c>
-      <c r="J221" s="5" t="n">
-        <v>0.039522</v>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>0.026047</v>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v>0.021468</v>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v>0.017622</v>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v>0.020191</v>
-      </c>
-      <c r="O221" s="5" t="n">
-        <v>0.027148</v>
-      </c>
-      <c r="P221" s="5" t="n">
-        <v>0.012514</v>
+      <c r="G221" s="5" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Management fees 7</t>
+          <t>Write-down of exploration and evaluation assets (Note 6)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -23129,10 +22861,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G222" s="5" t="n">
+        <v>12.186775</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -23169,108 +22899,116 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O222" s="5" t="n">
-        <v>0.3095</v>
-      </c>
-      <c r="P222" s="5" t="n">
-        <v>0.3885</v>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" s="5" t="n">
-        <v>0.041377</v>
-      </c>
-      <c r="I223" s="5" t="n">
-        <v>0.063253</v>
-      </c>
-      <c r="J223" s="5" t="n">
-        <v>0.046349</v>
-      </c>
-      <c r="K223" s="5" t="n">
-        <v>0.050184</v>
-      </c>
-      <c r="L223" s="5" t="n">
-        <v>0.059858</v>
-      </c>
-      <c r="M223" s="5" t="n">
-        <v>0.061992</v>
-      </c>
-      <c r="N223" s="5" t="n">
-        <v>0.052665</v>
-      </c>
-      <c r="O223" s="5" t="n">
-        <v>0.063929</v>
-      </c>
-      <c r="P223" s="5" t="n">
-        <v>0.058935</v>
+          <t>Proceeds from sale of equipment</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
+        <v>0.04064</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>0.011565</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Project investigation</t>
+          <t>Proceeds from government exploration tax credits (Note 6)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E224" s="5" t="n">
+        <v>0.56484</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G224" s="5" t="n">
+        <v>0.05987</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -23292,48 +23030,58 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L224" s="5" t="n">
-        <v>0.021868</v>
-      </c>
-      <c r="M224" s="5" t="n">
-        <v>0.298402</v>
-      </c>
-      <c r="N224" s="5" t="n">
-        <v>0.179108</v>
-      </c>
-      <c r="O224" s="5" t="n">
-        <v>0.0541</v>
-      </c>
-      <c r="P224" s="5" t="n">
-        <v>0.018657</v>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Office and rent expenses</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="n">
+        <v>-1.319086</v>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>-0.72848</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -23360,48 +23108,54 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L225" s="5" t="n">
-        <v>0.018327</v>
-      </c>
-      <c r="M225" s="5" t="n">
-        <v>0.042007</v>
-      </c>
-      <c r="N225" s="5" t="n">
-        <v>0.052039</v>
-      </c>
-      <c r="O225" s="5" t="n">
-        <v>0.05629</v>
-      </c>
-      <c r="P225" s="5" t="n">
-        <v>0.070781</v>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Share-based compensation 6, 7</t>
+          <t>Loss from disposal of equipment</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E226" s="5" t="n">
+        <v>0.163768</v>
+      </c>
+      <c r="F226" s="5" t="n">
+        <v>0.00262</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -23448,31 +23202,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P226" s="5" t="n">
-        <v>0.132731</v>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Shareholder relations</t>
+          <t>Supplies inventory</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E227" s="5" t="n">
+        <v>0.026479</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23484,32 +23238,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H227" s="5" t="n">
-        <v>0.00133</v>
-      </c>
-      <c r="I227" s="5" t="n">
-        <v>0.028902</v>
-      </c>
-      <c r="J227" s="5" t="n">
-        <v>0.012513</v>
-      </c>
-      <c r="K227" s="5" t="n">
-        <v>0.009140000000000001</v>
-      </c>
-      <c r="L227" s="5" t="n">
-        <v>0.009077999999999999</v>
-      </c>
-      <c r="M227" s="5" t="n">
-        <v>0.003857</v>
-      </c>
-      <c r="N227" s="5" t="n">
-        <v>0.003413</v>
-      </c>
-      <c r="O227" s="5" t="n">
-        <v>0.003461</v>
-      </c>
-      <c r="P227" s="5" t="n">
-        <v>0.006227</v>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -23525,12 +23297,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Amortization $</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -23568,20 +23340,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L228" s="5" t="n">
-        <v>0.002412</v>
-      </c>
-      <c r="M228" s="5" t="n">
-        <v>0.007718</v>
-      </c>
-      <c r="N228" s="5" t="n">
-        <v>0.071829</v>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O228" s="5" t="n">
-        <v>0.03477</v>
-      </c>
-      <c r="P228" s="5" t="n">
-        <v>0.070031</v>
+        <v>0.005107</v>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -23597,12 +23377,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Consulting fees 7</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -23620,32 +23400,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H229" s="5" t="n">
-        <v>0.323921</v>
-      </c>
-      <c r="I229" s="5" t="n">
-        <v>0.456954</v>
-      </c>
-      <c r="J229" s="5" t="n">
-        <v>0.848163</v>
-      </c>
-      <c r="K229" s="5" t="n">
-        <v>0.7179219999999999</v>
-      </c>
-      <c r="L229" s="5" t="n">
-        <v>0.579697</v>
-      </c>
-      <c r="M229" s="5" t="n">
-        <v>0.906186</v>
-      </c>
-      <c r="N229" s="5" t="n">
-        <v>0.722209</v>
-      </c>
-      <c r="O229" s="5" t="n">
-        <v>0.570305</v>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P229" s="5" t="n">
-        <v>0.921376</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="230">
@@ -23656,17 +23452,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Director fees 7</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -23720,10 +23516,10 @@
         </is>
       </c>
       <c r="O230" s="5" t="n">
-        <v>0.114035</v>
+        <v>0.016</v>
       </c>
       <c r="P230" s="5" t="n">
-        <v>0.058106</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="231">
@@ -23734,15 +23530,19 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Gain on disposal of investments 4</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>Filing and transfer agent</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -23758,48 +23558,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H231" s="5" t="n">
+        <v>0.012547</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>0.016651</v>
+      </c>
+      <c r="J231" s="5" t="n">
+        <v>0.039522</v>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>0.026047</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>0.021468</v>
+      </c>
+      <c r="M231" s="5" t="n">
+        <v>0.017622</v>
+      </c>
+      <c r="N231" s="5" t="n">
+        <v>0.020191</v>
+      </c>
+      <c r="O231" s="5" t="n">
+        <v>0.027148</v>
       </c>
       <c r="P231" s="5" t="n">
-        <v>0.234118</v>
+        <v>0.012514</v>
       </c>
     </row>
     <row r="232">
@@ -23810,15 +23594,19 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investments 4</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
+          <t>Management fees 7</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -23870,10 +23658,10 @@
         </is>
       </c>
       <c r="O232" s="5" t="n">
-        <v>-0.83622</v>
+        <v>0.3095</v>
       </c>
       <c r="P232" s="5" t="n">
-        <v>0.45123</v>
+        <v>0.3885</v>
       </c>
     </row>
     <row r="233">
@@ -23884,15 +23672,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 3</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -23908,46 +23700,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H233" s="5" t="n">
+        <v>0.041377</v>
+      </c>
+      <c r="I233" s="5" t="n">
+        <v>0.063253</v>
+      </c>
+      <c r="J233" s="5" t="n">
+        <v>0.046349</v>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>0.050184</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>0.059858</v>
+      </c>
+      <c r="M233" s="5" t="n">
+        <v>0.061992</v>
+      </c>
+      <c r="N233" s="5" t="n">
+        <v>0.052665</v>
       </c>
       <c r="O233" s="5" t="n">
-        <v>-1e-06</v>
+        <v>0.063929</v>
       </c>
       <c r="P233" s="5" t="n">
-        <v>-0.424427</v>
+        <v>0.058935</v>
       </c>
     </row>
     <row r="234">
@@ -23958,12 +23736,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Total other items</t>
+          <t>Project investigation</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -24002,26 +23780,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L234" s="5" t="n">
+        <v>0.021868</v>
+      </c>
+      <c r="M234" s="5" t="n">
+        <v>0.298402</v>
+      </c>
+      <c r="N234" s="5" t="n">
+        <v>0.179108</v>
       </c>
       <c r="O234" s="5" t="n">
-        <v>-0.722186</v>
+        <v>0.0541</v>
       </c>
       <c r="P234" s="5" t="n">
-        <v>0.319027</v>
+        <v>0.018657</v>
       </c>
     </row>
     <row r="235">
@@ -24032,19 +23804,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Office and rent expenses</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -24080,26 +23848,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L235" s="5" t="n">
+        <v>0.018327</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>0.042007</v>
+      </c>
+      <c r="N235" s="5" t="n">
+        <v>0.052039</v>
       </c>
       <c r="O235" s="5" t="n">
-        <v>-1.292491</v>
+        <v>0.05629</v>
       </c>
       <c r="P235" s="5" t="n">
-        <v>-0.602349</v>
+        <v>0.070781</v>
       </c>
     </row>
     <row r="236">
@@ -24110,19 +23872,15 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share-based compensation 6, 7</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -24173,11 +23931,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O236" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P236" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.132731</v>
       </c>
     </row>
     <row r="237">
@@ -24188,19 +23948,15 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - Basic</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Shareholder relations</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -24216,46 +23972,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H237" s="5" t="n">
+        <v>0.00133</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>0.028902</v>
+      </c>
+      <c r="J237" s="5" t="n">
+        <v>0.012513</v>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>0.009140000000000001</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>0.009077999999999999</v>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>0.003857</v>
+      </c>
+      <c r="N237" s="5" t="n">
+        <v>0.003413</v>
       </c>
       <c r="O237" s="5" t="n">
-        <v>41.093141</v>
+        <v>0.003461</v>
       </c>
       <c r="P237" s="5" t="n">
-        <v>41.093141</v>
+        <v>0.006227</v>
       </c>
     </row>
     <row r="238">
@@ -24271,12 +24013,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Amortization 3 $</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -24314,26 +24056,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L238" s="5" t="n">
+        <v>0.002412</v>
+      </c>
+      <c r="M238" s="5" t="n">
+        <v>0.007718</v>
       </c>
       <c r="N238" s="5" t="n">
-        <v>0.011464</v>
+        <v>0.071829</v>
       </c>
       <c r="O238" s="5" t="n">
-        <v>0.005107</v>
-      </c>
-      <c r="P238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03477</v>
+      </c>
+      <c r="P238" s="5" t="n">
+        <v>0.070031</v>
       </c>
     </row>
     <row r="239">
@@ -24349,10 +24085,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Director fees 8</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -24368,46 +24108,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H239" s="5" t="n">
+        <v>0.323921</v>
+      </c>
+      <c r="I239" s="5" t="n">
+        <v>0.456954</v>
+      </c>
+      <c r="J239" s="5" t="n">
+        <v>0.848163</v>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>0.7179219999999999</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>0.579697</v>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>0.906186</v>
       </c>
       <c r="N239" s="5" t="n">
-        <v>0.012</v>
+        <v>0.722209</v>
       </c>
       <c r="O239" s="5" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.570305</v>
+      </c>
+      <c r="P239" s="5" t="n">
+        <v>0.921376</v>
       </c>
     </row>
     <row r="240">
@@ -24418,17 +24144,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Management fees 8</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -24476,16 +24202,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N240" s="5" t="n">
-        <v>0.3195</v>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O240" s="5" t="n">
-        <v>0.3095</v>
-      </c>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.114035</v>
+      </c>
+      <c r="P240" s="5" t="n">
+        <v>0.058106</v>
       </c>
     </row>
     <row r="241">
@@ -24496,19 +24222,15 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Gain on disposal of investments 4</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -24524,36 +24246,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H241" s="5" t="n">
-        <v>0.003309</v>
-      </c>
-      <c r="I241" s="5" t="n">
-        <v>0.002225</v>
-      </c>
-      <c r="J241" s="5" t="n">
-        <v>0.004007</v>
-      </c>
-      <c r="K241" s="5" t="n">
-        <v>0.00478</v>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M241" s="5" t="n">
-        <v>0.026182</v>
-      </c>
-      <c r="N241" s="5" t="n">
-        <v>0.126461</v>
-      </c>
-      <c r="O241" s="5" t="n">
-        <v>0.114035</v>
-      </c>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P241" s="5" t="n">
+        <v>0.234118</v>
       </c>
     </row>
     <row r="242">
@@ -24564,12 +24298,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investments 5</t>
+          <t>Fair value adjustment on investments 4</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -24618,16 +24352,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N242" s="5" t="n">
-        <v>-2.01453</v>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O242" s="5" t="n">
         <v>-0.83622</v>
       </c>
-      <c r="P242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P242" s="5" t="n">
+        <v>0.45123</v>
       </c>
     </row>
     <row r="243">
@@ -24638,12 +24372,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 4</t>
+          <t>Impairment of exploration and evaluation assets 3</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -24692,16 +24426,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N243" s="5" t="n">
-        <v>-0.06647400000000001</v>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O243" s="5" t="n">
         <v>-1e-06</v>
       </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P243" s="5" t="n">
+        <v>-0.424427</v>
       </c>
     </row>
     <row r="244">
@@ -24712,19 +24446,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Total other items</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -24740,34 +24470,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H244" s="5" t="n">
-        <v>0.010909</v>
-      </c>
-      <c r="I244" s="5" t="n">
-        <v>0.046647</v>
-      </c>
-      <c r="J244" s="5" t="n">
-        <v>0.003507</v>
-      </c>
-      <c r="K244" s="5" t="n">
-        <v>0.34558</v>
-      </c>
-      <c r="L244" s="5" t="n">
-        <v>1.376211</v>
-      </c>
-      <c r="M244" s="5" t="n">
-        <v>2.380492</v>
-      </c>
-      <c r="N244" s="5" t="n">
-        <v>1.954543</v>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O244" s="5" t="n">
-        <v>0.722186</v>
-      </c>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.722186</v>
+      </c>
+      <c r="P244" s="5" t="n">
+        <v>0.319027</v>
       </c>
     </row>
     <row r="245">
@@ -24778,7 +24520,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -24831,19 +24573,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M245" s="5" t="n">
-        <v>-3.286678</v>
-      </c>
-      <c r="N245" s="5" t="n">
-        <v>-2.676752</v>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O245" s="5" t="n">
         <v>-1.292491</v>
       </c>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P245" s="5" t="n">
+        <v>-0.602349</v>
       </c>
     </row>
     <row r="246">
@@ -24854,7 +24598,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -24892,30 +24636,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J246" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="K246" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M246" s="5" t="n">
-        <v>-1.1e-07</v>
-      </c>
-      <c r="N246" s="5" t="n">
-        <v>-7e-08</v>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O246" s="5" t="n">
         <v>-3e-08</v>
       </c>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P246" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="247">
@@ -24926,7 +24676,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -24974,22 +24724,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L247" s="5" t="n">
-        <v>24.076964</v>
-      </c>
-      <c r="M247" s="5" t="n">
-        <v>29.31415</v>
-      </c>
-      <c r="N247" s="5" t="n">
-        <v>41.093141</v>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O247" s="5" t="n">
         <v>41.093141</v>
       </c>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P247" s="5" t="n">
+        <v>41.093141</v>
       </c>
     </row>
     <row r="248">
@@ -25005,10 +24759,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Accretion of interest (Note 7) $</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>Amortization 3 $</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -25044,21 +24802,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L248" s="5" t="n">
-        <v>0.068296</v>
-      </c>
-      <c r="M248" s="5" t="n">
-        <v>0.018792</v>
-      </c>
-      <c r="N248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="5" t="n">
+        <v>0.011464</v>
+      </c>
+      <c r="O248" s="5" t="n">
+        <v>0.005107</v>
       </c>
       <c r="P248" t="inlineStr">
         <is>
@@ -25079,12 +24837,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Amortization (Note 3)</t>
+          <t>Director fees 8</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -25102,33 +24860,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H249" s="5" t="n">
-        <v>0.058774</v>
-      </c>
-      <c r="I249" s="5" t="n">
-        <v>0.050174</v>
-      </c>
-      <c r="J249" s="5" t="n">
-        <v>0.058346</v>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L249" s="5" t="n">
-        <v>0.017105</v>
-      </c>
-      <c r="M249" s="5" t="n">
-        <v>0.021784</v>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N249" s="5" t="n">
-        <v>0.011464</v>
-      </c>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012</v>
+      </c>
+      <c r="O249" s="5" t="n">
+        <v>0.016</v>
       </c>
       <c r="P249" t="inlineStr">
         <is>
@@ -25149,10 +24915,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Director fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Management fees 8</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -25188,19 +24958,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L250" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="M250" s="5" t="n">
-        <v>0.012</v>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N250" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3195</v>
+      </c>
+      <c r="O250" s="5" t="n">
+        <v>0.3095</v>
       </c>
       <c r="P250" t="inlineStr">
         <is>
@@ -25221,12 +24993,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -25244,35 +25016,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H251" s="5" t="n">
+        <v>0.003309</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>0.002225</v>
       </c>
       <c r="J251" s="5" t="n">
-        <v>0.168</v>
+        <v>0.004007</v>
       </c>
       <c r="K251" s="5" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="L251" s="5" t="n">
-        <v>0.196</v>
+        <v>0.00478</v>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M251" s="5" t="n">
-        <v>0.256</v>
+        <v>0.026182</v>
       </c>
       <c r="N251" s="5" t="n">
-        <v>0.3195</v>
-      </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.126461</v>
+      </c>
+      <c r="O251" s="5" t="n">
+        <v>0.114035</v>
       </c>
       <c r="P251" t="inlineStr">
         <is>
@@ -25293,7 +25061,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Salary and benefit</t>
+          <t>Fair value adjustment on investments 5</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
@@ -25332,21 +25100,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L252" s="5" t="n">
-        <v>0.059214</v>
-      </c>
-      <c r="M252" s="5" t="n">
-        <v>0.005301</v>
-      </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="5" t="n">
+        <v>-2.01453</v>
+      </c>
+      <c r="O252" s="5" t="n">
+        <v>-0.83622</v>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -25367,7 +25135,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Share based compensation (Notes 8 and 9)</t>
+          <t>Impairment of exploration and evaluation assets 4</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -25406,21 +25174,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L253" s="5" t="n">
-        <v>0.091071</v>
-      </c>
-      <c r="M253" s="5" t="n">
-        <v>0.160711</v>
-      </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="5" t="n">
+        <v>-0.06647400000000001</v>
+      </c>
+      <c r="O253" s="5" t="n">
+        <v>-1e-06</v>
       </c>
       <c r="P253" t="inlineStr">
         <is>
@@ -25441,10 +25209,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investments (Note 5)</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -25460,39 +25232,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H254" s="5" t="n">
+        <v>0.010909</v>
+      </c>
+      <c r="I254" s="5" t="n">
+        <v>0.046647</v>
+      </c>
+      <c r="J254" s="5" t="n">
+        <v>0.003507</v>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>0.34558</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>0.74432</v>
+        <v>1.376211</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>-2.573415</v>
+        <v>2.380492</v>
       </c>
       <c r="N254" s="5" t="n">
-        <v>-2.01453</v>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.954543</v>
+      </c>
+      <c r="O254" s="5" t="n">
+        <v>0.722186</v>
       </c>
       <c r="P254" t="inlineStr">
         <is>
@@ -25513,10 +25275,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Gain on disposal of investment (Note 5)</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -25552,21 +25318,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L255" s="5" t="n">
-        <v>0.443591</v>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M255" s="5" t="n">
-        <v>0.166741</v>
-      </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.286678</v>
+      </c>
+      <c r="N255" s="5" t="n">
+        <v>-2.676752</v>
+      </c>
+      <c r="O255" s="5" t="n">
+        <v>-1.292491</v>
       </c>
       <c r="P255" t="inlineStr">
         <is>
@@ -25587,10 +25351,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 4)</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -25616,33 +25384,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J256" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M256" s="5" t="n">
+        <v>-1.1e-07</v>
       </c>
       <c r="N256" s="5" t="n">
-        <v>-0.06647400000000001</v>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7e-08</v>
+      </c>
+      <c r="O256" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="P256" t="inlineStr">
         <is>
@@ -25663,10 +25423,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Gain on dilution of investment in equity investment (Note 6)</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding - Basic</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -25703,22 +25467,16 @@
         </is>
       </c>
       <c r="L257" s="5" t="n">
-        <v>0.565662</v>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>24.076964</v>
+      </c>
+      <c r="M257" s="5" t="n">
+        <v>29.31415</v>
+      </c>
+      <c r="N257" s="5" t="n">
+        <v>41.093141</v>
+      </c>
+      <c r="O257" s="5" t="n">
+        <v>41.093141</v>
       </c>
       <c r="P257" t="inlineStr">
         <is>
@@ -25739,7 +25497,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Share of loss on equity investment (Note 6)</t>
+          <t>Accretion of interest (Note 7) $</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -25779,12 +25537,10 @@
         </is>
       </c>
       <c r="L258" s="5" t="n">
-        <v>-0.326008</v>
-      </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.068296</v>
+      </c>
+      <c r="M258" s="5" t="n">
+        <v>0.018792</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -25815,10 +25571,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets (Note 4)</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
+          <t>Amortization (Note 3)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -25834,20 +25594,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H259" s="5" t="n">
+        <v>0.058774</v>
+      </c>
+      <c r="I259" s="5" t="n">
+        <v>0.050174</v>
+      </c>
+      <c r="J259" s="5" t="n">
+        <v>0.058346</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -25855,17 +25609,13 @@
         </is>
       </c>
       <c r="L259" s="5" t="n">
-        <v>-0.051354</v>
-      </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.017105</v>
+      </c>
+      <c r="M259" s="5" t="n">
+        <v>0.021784</v>
+      </c>
+      <c r="N259" s="5" t="n">
+        <v>0.011464</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -25891,12 +25641,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Income and comprehensive income (loss) for the year</t>
+          <t>Director fees (Note 9)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -25935,15 +25685,13 @@
         </is>
       </c>
       <c r="L260" s="5" t="n">
-        <v>0.7965140000000001</v>
+        <v>0.015</v>
       </c>
       <c r="M260" s="5" t="n">
-        <v>-3.286678</v>
-      </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012</v>
+      </c>
+      <c r="N260" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -25969,10 +25717,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Basic income (loss) per common share $</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>Management fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -25998,26 +25750,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J261" s="5" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>0.168</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.196</v>
       </c>
       <c r="M261" s="5" t="n">
-        <v>-1.1e-07</v>
-      </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.256</v>
+      </c>
+      <c r="N261" s="5" t="n">
+        <v>0.3195</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -26043,7 +25789,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Diluted income (loss) per common share $</t>
+          <t>Salary and benefit</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -26083,10 +25829,10 @@
         </is>
       </c>
       <c r="L262" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.059214</v>
       </c>
       <c r="M262" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>0.005301</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
@@ -26112,19 +25858,15 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding -</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Share based compensation (Notes 8 and 9)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -26161,10 +25903,10 @@
         </is>
       </c>
       <c r="L263" s="5" t="n">
-        <v>28.926964</v>
+        <v>0.091071</v>
       </c>
       <c r="M263" s="5" t="n">
-        <v>29.31415</v>
+        <v>0.160711</v>
       </c>
       <c r="N263" t="inlineStr">
         <is>
@@ -26195,7 +25937,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation (Note 6) $</t>
+          <t>Fair value adjustment on investments (Note 5)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -26224,26 +25966,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J264" s="5" t="n">
-        <v>0.056242</v>
-      </c>
-      <c r="K264" s="5" t="n">
-        <v>0.058732</v>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>0.74432</v>
+      </c>
+      <c r="M264" s="5" t="n">
+        <v>-2.573415</v>
+      </c>
+      <c r="N264" s="5" t="n">
+        <v>-2.01453</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
@@ -26269,7 +26009,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Accretion of interest (Note 7)</t>
+          <t>Gain on disposal of investment (Note 5)</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -26303,18 +26043,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K265" s="5" t="n">
-        <v>0.03716</v>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>0.443591</v>
+      </c>
+      <c r="M265" s="5" t="n">
+        <v>0.166741</v>
       </c>
       <c r="N265" t="inlineStr">
         <is>
@@ -26345,14 +26083,10 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Amortization (Note 4)</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Impairment of exploration and evaluation assets (Note 4)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -26378,11 +26112,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J266" s="5" t="n">
-        <v>0.058346</v>
-      </c>
-      <c r="K266" s="5" t="n">
-        <v>0.046755</v>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -26394,10 +26132,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N266" s="5" t="n">
+        <v>-0.06647400000000001</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -26423,14 +26159,10 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Gain on dilution of investment in equity investment (Note 6)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -26451,21 +26183,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I267" s="5" t="n">
-        <v>0.026572</v>
-      </c>
-      <c r="J267" s="5" t="n">
-        <v>0.03386</v>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L267" s="5" t="n">
+        <v>0.565662</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
@@ -26501,7 +26235,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Loan interest (Note 9)</t>
+          <t>Share of loss on equity investment (Note 6)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -26530,18 +26264,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J268" s="5" t="n">
-        <v>0.00073</v>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L268" s="5" t="n">
+        <v>-0.326008</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
@@ -26577,7 +26311,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Project investigation (Note 15)</t>
+          <t>Write-off of exploration and evaluation assets (Note 4)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -26611,13 +26345,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K269" s="5" t="n">
-        <v>0.126642</v>
-      </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>-0.051354</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
@@ -26653,10 +26387,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Rent and office expenses (Note 9)</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Income and comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -26682,21 +26420,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J270" s="5" t="n">
-        <v>0.019652</v>
-      </c>
-      <c r="K270" s="5" t="n">
-        <v>0.02923</v>
-      </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>0.7965140000000001</v>
+      </c>
+      <c r="M270" s="5" t="n">
+        <v>-3.286678</v>
       </c>
       <c r="N270" t="inlineStr">
         <is>
@@ -26727,7 +26465,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 8)</t>
+          <t>Basic income (loss) per common share $</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -26756,21 +26494,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J271" s="5" t="n">
-        <v>0.189731</v>
-      </c>
-      <c r="K271" s="5" t="n">
-        <v>0.118614</v>
-      </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="M271" s="5" t="n">
+        <v>-1.1e-07</v>
       </c>
       <c r="N271" t="inlineStr">
         <is>
@@ -26801,7 +26539,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Camp maintenance</t>
+          <t>Diluted income (loss) per common share $</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -26820,27 +26558,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H272" s="5" t="n">
-        <v>0.034775</v>
-      </c>
-      <c r="I272" s="5" t="n">
-        <v>0.073458</v>
-      </c>
-      <c r="J272" s="5" t="n">
-        <v>0.223218</v>
-      </c>
-      <c r="K272" s="5" t="n">
-        <v>0.047418</v>
-      </c>
-      <c r="L272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="M272" s="5" t="n">
+        <v>-1.1e-07</v>
       </c>
       <c r="N272" t="inlineStr">
         <is>
@@ -26866,15 +26608,19 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of common shares outstanding -</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investments (Note 3)</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Diluted</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -26905,18 +26651,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K273" s="5" t="n">
-        <v>0.3492</v>
-      </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>28.926964</v>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>29.31415</v>
       </c>
       <c r="N273" t="inlineStr">
         <is>
@@ -26947,7 +26691,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Write-off of receivables</t>
+          <t>Accretion of asset retirement obligation (Note 6) $</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -26976,13 +26720,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J274" s="5" t="n">
+        <v>0.056242</v>
       </c>
       <c r="K274" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.058732</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -27023,14 +26765,10 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Accretion of interest (Note 7)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -27056,13 +26794,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J275" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>0.03716</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -27103,12 +26841,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Amortization (Note 4)</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -27137,10 +26875,10 @@
         </is>
       </c>
       <c r="J276" s="5" t="n">
-        <v>-0.844656</v>
+        <v>0.058346</v>
       </c>
       <c r="K276" s="5" t="n">
-        <v>-0.372342</v>
+        <v>0.046755</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -27176,15 +26914,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -27205,16 +26947,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I277" s="5" t="n">
+        <v>0.026572</v>
       </c>
       <c r="J277" s="5" t="n">
-        <v>13.556416</v>
-      </c>
-      <c r="K277" s="5" t="n">
-        <v>14.839813</v>
+        <v>0.03386</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -27255,7 +26997,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation (Note 5) $</t>
+          <t>Loan interest (Note 9)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -27274,14 +27016,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H278" s="5" t="n">
-        <v>0.03513</v>
-      </c>
-      <c r="I278" s="5" t="n">
-        <v>0.031793</v>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J278" s="5" t="n">
-        <v>0.056242</v>
+        <v>0.00073</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -27327,7 +27073,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Director and executive fees (Note 7)</t>
+          <t>Project investigation (Note 15)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -27346,21 +27092,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H279" s="5" t="n">
-        <v>0.012334</v>
-      </c>
-      <c r="I279" s="5" t="n">
-        <v>0.0015</v>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K279" s="5" t="n">
+        <v>0.126642</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -27401,10 +27149,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Loan interest (Note 7)</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Rent and office expenses (Note 9)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -27420,19 +27172,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H280" s="5" t="n">
-        <v>0.004085</v>
-      </c>
-      <c r="I280" s="5" t="n">
-        <v>0.020723</v>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J280" s="5" t="n">
-        <v>0.00073</v>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019652</v>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>0.02923</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -27473,14 +27227,10 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Management fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share based compensation (Note 8)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -27501,16 +27251,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I281" s="5" t="n">
-        <v>0.098</v>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J281" s="5" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.189731</v>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>0.118614</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -27551,7 +27301,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Rent and office expenses (Note 7)</t>
+          <t>Camp maintenance</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -27571,18 +27321,16 @@
         </is>
       </c>
       <c r="H282" s="5" t="n">
-        <v>0.026324</v>
+        <v>0.034775</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>0.019994</v>
+        <v>0.073458</v>
       </c>
       <c r="J282" s="5" t="n">
-        <v>0.019652</v>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.223218</v>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>0.047418</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -27623,14 +27371,10 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Salaries and benefits (Note 7)</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Fair value adjustment on investments (Note 3)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -27646,21 +27390,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H283" s="5" t="n">
-        <v>0.097245</v>
-      </c>
-      <c r="I283" s="5" t="n">
-        <v>0.025934</v>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K283" s="5" t="n">
+        <v>0.3492</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -27701,7 +27447,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 6)</t>
+          <t>Write-off of receivables</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -27730,13 +27476,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J284" s="5" t="n">
-        <v>0.189731</v>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -27777,10 +27523,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -27801,13 +27551,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I285" s="5" t="n">
-        <v>0.016359</v>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J285" s="5" t="n">
+        <v>-0.0005</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -27853,12 +27603,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Gain (loss) on foreign exchange</t>
+          <t>Loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -27881,16 +27631,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I286" s="5" t="n">
-        <v>0.004571</v>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J286" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.844656</v>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>-0.372342</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -27926,12 +27676,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Extinguishment of accounts payable</t>
+          <t>Weighted average number of common shares outstanding - Basic and diluted</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -27955,18 +27705,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I287" s="5" t="n">
-        <v>0.024283</v>
-      </c>
-      <c r="J287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J287" s="5" t="n">
+        <v>13.556416</v>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>14.839813</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -28007,7 +27755,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Loss on dissolution of subsidiary</t>
+          <t>Accretion of asset retirement obligation (Note 5) $</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -28026,18 +27774,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H288" s="5" t="n">
+        <v>0.03513</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>-0.000791</v>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031793</v>
+      </c>
+      <c r="J288" s="5" t="n">
+        <v>0.056242</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -28083,14 +27827,10 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Director and executive fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -28107,13 +27847,15 @@
         </is>
       </c>
       <c r="H289" s="5" t="n">
-        <v>-0.313012</v>
+        <v>0.012334</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>-0.410307</v>
-      </c>
-      <c r="J289" s="5" t="n">
-        <v>-0.844656</v>
+        <v>0.0015</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -28154,12 +27896,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustments</t>
+          <t>Loan interest (Note 7)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -28179,15 +27921,13 @@
         </is>
       </c>
       <c r="H290" s="5" t="n">
-        <v>-0.000485</v>
+        <v>0.004085</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>-0.004926</v>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020723</v>
+      </c>
+      <c r="J290" s="5" t="n">
+        <v>0.00073</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -28228,17 +27968,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year</t>
+          <t>Management fees (Note 7)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -28256,14 +27996,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H291" s="5" t="n">
-        <v>-0.313497</v>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I291" s="5" t="n">
-        <v>-0.415233</v>
+        <v>0.098</v>
       </c>
       <c r="J291" s="5" t="n">
-        <v>-0.844656</v>
+        <v>0.168</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -28304,17 +28046,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Rent and office expenses (Note 7)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -28333,13 +28075,13 @@
         </is>
       </c>
       <c r="H292" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.026324</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.019994</v>
       </c>
       <c r="J292" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.019652</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -28380,17 +28122,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Salaries and benefits (Note 7)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -28409,13 +28151,15 @@
         </is>
       </c>
       <c r="H293" s="5" t="n">
-        <v>7.594813</v>
+        <v>0.097245</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>7.594813</v>
-      </c>
-      <c r="J293" s="5" t="n">
-        <v>13.556416</v>
+        <v>0.025934</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -28461,14 +28205,10 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Consulting fee</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share based compensation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -28489,13 +28229,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I294" s="5" t="n">
-        <v>0.026572</v>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J294" s="5" t="n">
+        <v>0.189731</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -28541,7 +28281,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment (Note 3)</t>
+          <t>Gain on disposal of equipment</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -28560,8 +28300,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H295" s="5" t="n">
-        <v>0.0076</v>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I295" s="5" t="n">
         <v>0.016359</v>
@@ -28615,12 +28357,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Gain on foreign exchange</t>
+          <t>Gain (loss) on foreign exchange</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -28646,10 +28388,8 @@
       <c r="I296" s="5" t="n">
         <v>0.004571</v>
       </c>
-      <c r="J296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J296" s="5" t="n">
+        <v>-0.0005</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -28695,7 +28435,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Loss on dissolution of subsidiary (Note 1)</t>
+          <t>Extinguishment of accounts payable</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -28720,7 +28460,7 @@
         </is>
       </c>
       <c r="I297" s="5" t="n">
-        <v>-0.000791</v>
+        <v>0.024283</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -28766,12 +28506,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Accretion of asset retirement obligation $</t>
+          <t>Loss on dissolution of subsidiary</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -28785,16 +28525,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G298" s="5" t="n">
-        <v>0.0287</v>
-      </c>
-      <c r="H298" s="5" t="n">
-        <v>0.03513</v>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I298" s="5" t="n">
+        <v>-0.000791</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -28840,17 +28582,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -28863,21 +28605,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G299" s="5" t="n">
-        <v>0.000828</v>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H299" s="5" t="n">
-        <v>0.058774</v>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.313012</v>
+      </c>
+      <c r="I299" s="5" t="n">
+        <v>-0.410307</v>
+      </c>
+      <c r="J299" s="5" t="n">
+        <v>-0.844656</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -28918,12 +28658,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Director and executive fees</t>
+          <t>Cumulative translation adjustments</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -28937,16 +28677,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G300" s="5" t="n">
-        <v>0.156506</v>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H300" s="5" t="n">
-        <v>0.012334</v>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000485</v>
+      </c>
+      <c r="I300" s="5" t="n">
+        <v>-0.004926</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -28992,17 +28732,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Filing fees and transfer agent</t>
+          <t>Comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -29015,21 +28755,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G301" s="5" t="n">
-        <v>0.019441</v>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H301" s="5" t="n">
-        <v>0.012547</v>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.313497</v>
+      </c>
+      <c r="I301" s="5" t="n">
+        <v>-0.415233</v>
+      </c>
+      <c r="J301" s="5" t="n">
+        <v>-0.844656</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -29070,17 +28808,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Professional and consulting fees</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -29093,21 +28831,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G302" s="5" t="n">
-        <v>0.156428</v>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H302" s="5" t="n">
-        <v>0.041377</v>
-      </c>
-      <c r="I302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="I302" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="J302" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -29148,15 +28884,19 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Rent and office expenses</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -29167,21 +28907,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G303" s="5" t="n">
-        <v>0.043702</v>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H303" s="5" t="n">
-        <v>0.026324</v>
-      </c>
-      <c r="I303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.594813</v>
+      </c>
+      <c r="I303" s="5" t="n">
+        <v>7.594813</v>
+      </c>
+      <c r="J303" s="5" t="n">
+        <v>13.556416</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -29222,17 +28960,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Consulting fee</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -29245,16 +28983,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G304" s="5" t="n">
-        <v>0.131237</v>
-      </c>
-      <c r="H304" s="5" t="n">
-        <v>0.097245</v>
-      </c>
-      <c r="I304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I304" s="5" t="n">
+        <v>0.026572</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -29300,12 +29040,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Shareholder relations</t>
+          <t>Gain on disposal of equipment (Note 3)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -29319,16 +29059,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G305" s="5" t="n">
-        <v>0.00477</v>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H305" s="5" t="n">
-        <v>0.00133</v>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0076</v>
+      </c>
+      <c r="I305" s="5" t="n">
+        <v>0.016359</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -29374,15 +29114,19 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Travel and others</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Gain on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -29393,18 +29137,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G306" s="5" t="n">
-        <v>0.001726</v>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I306" s="5" t="n">
+        <v>0.004571</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -29450,12 +29194,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Camp maintenance (Note 9(b))</t>
+          <t>Loss on dissolution of subsidiary (Note 1)</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -29469,16 +29213,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G307" s="5" t="n">
-        <v>0.116111</v>
-      </c>
-      <c r="H307" s="5" t="n">
-        <v>0.034775</v>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" s="5" t="n">
+        <v>-0.000791</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -29529,27 +29275,21 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Community relations</t>
+          <t>Accretion of asset retirement obligation $</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E308" s="5" t="n">
+        <v>0.035675</v>
+      </c>
+      <c r="F308" s="5" t="n">
+        <v>0.038687</v>
       </c>
       <c r="G308" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0287</v>
+      </c>
+      <c r="H308" s="5" t="n">
+        <v>0.03513</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -29605,29 +29345,25 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>0.003625</v>
+      </c>
+      <c r="F309" s="5" t="n">
+        <v>0.002414</v>
       </c>
       <c r="G309" s="5" t="n">
-        <v>0.729449</v>
+        <v>0.000828</v>
       </c>
       <c r="H309" s="5" t="n">
-        <v>0.319836</v>
+        <v>0.058774</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -29678,34 +29414,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Director and executive fees</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" s="5" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="F310" s="5" t="n">
+        <v>0.222</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>0.006469</v>
+        <v>0.156506</v>
       </c>
       <c r="H310" s="5" t="n">
-        <v>0.003309</v>
+        <v>0.012334</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -29756,36 +29484,30 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Other income (Note 10)</t>
+          <t>Filing fees and transfer agent</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="n">
+        <v>0.022159</v>
+      </c>
+      <c r="F311" s="5" t="n">
+        <v>0.019471</v>
       </c>
       <c r="G311" s="5" t="n">
-        <v>0.066176</v>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019441</v>
+      </c>
+      <c r="H311" s="5" t="n">
+        <v>0.012547</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -29836,32 +29558,30 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Finance costs (Note 8)</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr"/>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional and consulting fees</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="n">
+        <v>0.07755099999999999</v>
+      </c>
+      <c r="F312" s="5" t="n">
+        <v>0.108949</v>
+      </c>
+      <c r="G312" s="5" t="n">
+        <v>0.156428</v>
       </c>
       <c r="H312" s="5" t="n">
-        <v>-0.004085</v>
+        <v>0.041377</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -29912,30 +29632,30 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr"/>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Rent and office expenses</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="n">
+        <v>0.553979</v>
+      </c>
+      <c r="F313" s="5" t="n">
+        <v>0.329542</v>
       </c>
       <c r="G313" s="5" t="n">
-        <v>0.009233</v>
+        <v>0.043702</v>
       </c>
       <c r="H313" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.026324</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -29986,32 +29706,30 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Write-off of supplies inventory</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Salaries and benefits</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="n">
+        <v>0.442307</v>
+      </c>
+      <c r="F314" s="5" t="n">
+        <v>0.20576</v>
       </c>
       <c r="G314" s="5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.131237</v>
+      </c>
+      <c r="H314" s="5" t="n">
+        <v>0.097245</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -30062,12 +29780,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Write-off of equipment (Note 4)</t>
+          <t>Shareholder relations</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -30082,12 +29800,10 @@
         </is>
       </c>
       <c r="G315" s="5" t="n">
-        <v>-0.28699</v>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00477</v>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>0.00133</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -30138,12 +29854,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Write-down of exploration and evaluation assets (Note 5)</t>
+          <t>Travel and others</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -30152,13 +29868,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F316" s="5" t="n">
+        <v>0.002116</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>-12.186775</v>
+        <v>0.001726</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -30214,19 +29928,15 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Camp maintenance (Note 9(b))</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -30238,10 +29948,10 @@
         </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>-13.131336</v>
+        <v>0.116111</v>
       </c>
       <c r="H317" s="5" t="n">
-        <v>-0.313012</v>
+        <v>0.034775</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -30292,12 +30002,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustments</t>
+          <t>Community relations</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -30312,10 +30022,12 @@
         </is>
       </c>
       <c r="G318" s="5" t="n">
-        <v>0.003493</v>
-      </c>
-      <c r="H318" s="5" t="n">
-        <v>-0.000485</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -30366,17 +30078,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -30384,16 +30096,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F319" s="5" t="n">
+        <v>0.9352200000000001</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>-13.127843</v>
+        <v>0.729449</v>
       </c>
       <c r="H319" s="5" t="n">
-        <v>-0.313497</v>
+        <v>0.319836</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -30449,29 +30159,25 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="n">
+        <v>0.020197</v>
+      </c>
+      <c r="F320" s="5" t="n">
+        <v>0.015138</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.006469</v>
       </c>
       <c r="H320" s="5" t="n">
-        <v>0</v>
+        <v>0.003309</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -30527,66 +30233,2108 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
+          <t>Other income (Note 10)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="n">
+        <v>0.284533</v>
+      </c>
+      <c r="F321" s="5" t="n">
+        <v>0.19464</v>
+      </c>
+      <c r="G321" s="5" t="n">
+        <v>0.066176</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Finance costs (Note 8)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H322" s="5" t="n">
+        <v>-0.004085</v>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Gain on disposal of equipment</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="n">
+        <v>0.009233</v>
+      </c>
+      <c r="H323" s="5" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Write-off of supplies inventory</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Write-off of equipment (Note 4)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="n">
+        <v>-0.28699</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Write-down of exploration and evaluation assets (Note 5)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G326" s="5" t="n">
+        <v>-12.186775</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="n">
+        <v>-1.319086</v>
+      </c>
+      <c r="F327" s="5" t="n">
+        <v>-0.72848</v>
+      </c>
+      <c r="G327" s="5" t="n">
+        <v>-13.131336</v>
+      </c>
+      <c r="H327" s="5" t="n">
+        <v>-0.313012</v>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Cumulative translation adjustments</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" s="5" t="n">
+        <v>0.024587</v>
+      </c>
+      <c r="F328" s="5" t="n">
+        <v>0.003847</v>
+      </c>
+      <c r="G328" s="5" t="n">
+        <v>0.003493</v>
+      </c>
+      <c r="H328" s="5" t="n">
+        <v>-0.000485</v>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>-13.127843</v>
+      </c>
+      <c r="H329" s="5" t="n">
+        <v>-0.313497</v>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="H330" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
+      <c r="D331" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G321" s="5" t="n">
+      <c r="E331" s="5" t="n">
         <v>189.873268</v>
       </c>
-      <c r="H321" s="5" t="n">
+      <c r="F331" s="5" t="n">
         <v>189.873268</v>
       </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P321" t="inlineStr">
+      <c r="G331" s="5" t="n">
+        <v>189.873268</v>
+      </c>
+      <c r="H331" s="5" t="n">
+        <v>189.873268</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Shareholder and investor relations</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F332" s="5" t="n">
+        <v>0.006388</v>
+      </c>
+      <c r="G332" s="5" t="n">
+        <v>0.00477</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" s="5" t="n">
+        <v>0.009565000000000001</v>
+      </c>
+      <c r="F333" s="5" t="n">
+        <v>-0.000107</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Camp maintenance</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G334" s="5" t="n">
+        <v>0.116111</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Other income (Note 11)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F335" s="5" t="n">
+        <v>0.194222</v>
+      </c>
+      <c r="G335" s="5" t="n">
+        <v>0.066176</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Gain (loss) on disposal of equipment</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F336" s="5" t="n">
+        <v>-0.00262</v>
+      </c>
+      <c r="G336" s="5" t="n">
+        <v>0.009233</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Write-off of equipment (Note 5)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="n">
+        <v>-0.28699</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Write-down of exploration and evaluation assets (Note 6)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G338" s="5" t="n">
+        <v>-12.186775</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="n">
+        <v>-1.294499</v>
+      </c>
+      <c r="F339" s="5" t="n">
+        <v>-0.724633</v>
+      </c>
+      <c r="G339" s="5" t="n">
+        <v>-13.127843</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F340" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Bank charges and financing interests</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" s="5" t="n">
+        <v>0.002125</v>
+      </c>
+      <c r="F341" s="5" t="n">
+        <v>0.002034</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="n">
+        <v>0.041755</v>
+      </c>
+      <c r="F342" s="5" t="n">
+        <v>0.003233</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Loss from disposal of equipment</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" s="5" t="n">
+        <v>0.163768</v>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>0.00262</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Project investigation</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" s="5" t="n">
+        <v>0.022226</v>
+      </c>
+      <c r="F344" s="5" t="n">
+        <v>0.000242</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Shareholder information</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" s="5" t="n">
+        <v>0.003981</v>
+      </c>
+      <c r="F345" s="5" t="n">
+        <v>0.003155</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="n">
+        <v>0.008503</v>
+      </c>
+      <c r="F346" s="5" t="n">
+        <v>0.001874</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="n">
+        <v>-1.615219</v>
+      </c>
+      <c r="F347" s="5" t="n">
+        <v>-0.93784</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Foreign exchange (loss)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="n">
+        <v>-0.008597</v>
+      </c>
+      <c r="F348" s="5" t="n">
+        <v>-0.000418</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
         <is>
           <t>-</t>
         </is>
